--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -460,22 +470,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.80045</v>
+        <v>16.83405</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64037</v>
+        <v>16.40516</v>
       </c>
       <c r="E2" t="n">
-        <v>16.62377</v>
+        <v>16.74419</v>
       </c>
       <c r="F2" t="n">
-        <v>42.76502</v>
+        <v>55.01979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05085</v>
+        <v>41.87846</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84244</v>
+        <v>86.19868</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.83458</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.04823</v>
+        <v>16.90309</v>
       </c>
       <c r="D3" t="n">
-        <v>16.76093</v>
+        <v>16.34577</v>
       </c>
       <c r="E3" t="n">
-        <v>17.02203</v>
+        <v>16.50895</v>
       </c>
       <c r="F3" t="n">
-        <v>43.04423</v>
+        <v>56.15208</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05139</v>
+        <v>43.55168</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78046</v>
+        <v>85.60218999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.84271</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.70335</v>
+        <v>17.09036</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7117</v>
+        <v>16.68353</v>
       </c>
       <c r="E4" t="n">
-        <v>16.64794</v>
+        <v>16.79159</v>
       </c>
       <c r="F4" t="n">
-        <v>42.66265</v>
+        <v>56.92244</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05067</v>
+        <v>43.07792</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80316</v>
+        <v>85.4511</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.83917</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.83405</v>
+        <v>16.88334</v>
       </c>
       <c r="D5" t="n">
-        <v>16.40516</v>
+        <v>16.67352</v>
       </c>
       <c r="E5" t="n">
-        <v>16.74419</v>
+        <v>16.81424</v>
       </c>
       <c r="F5" t="n">
-        <v>42.01512</v>
+        <v>55.31293</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04986</v>
+        <v>41.96054</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84711</v>
+        <v>84.91614</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.78863</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.79103</v>
+        <v>16.62462</v>
       </c>
       <c r="D6" t="n">
-        <v>16.71502</v>
+        <v>16.46204</v>
       </c>
       <c r="E6" t="n">
-        <v>16.80127</v>
+        <v>16.59406</v>
       </c>
       <c r="F6" t="n">
-        <v>41.86111</v>
+        <v>54.20229</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05003</v>
+        <v>43.15947</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8377</v>
+        <v>85.45865999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.89179</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.21328</v>
+        <v>16.58069</v>
       </c>
       <c r="D7" t="n">
-        <v>16.71281</v>
+        <v>16.36175</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6363</v>
+        <v>16.487</v>
       </c>
       <c r="F7" t="n">
-        <v>42.99654</v>
+        <v>56.1369</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05148</v>
+        <v>43.10005</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83112</v>
+        <v>86.06652</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.81651</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89336</v>
+        <v>16.84381</v>
       </c>
       <c r="D8" t="n">
-        <v>16.97324</v>
+        <v>16.51626</v>
       </c>
       <c r="E8" t="n">
-        <v>16.92347</v>
+        <v>16.69004</v>
       </c>
       <c r="F8" t="n">
-        <v>42.72555</v>
+        <v>55.45028</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05103</v>
+        <v>42.23407</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83917</v>
+        <v>84.44436</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.83562</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.67352</v>
+        <v>16.93705</v>
       </c>
       <c r="D9" t="n">
-        <v>16.88334</v>
+        <v>16.36869</v>
       </c>
       <c r="E9" t="n">
-        <v>16.81424</v>
+        <v>16.41516</v>
       </c>
       <c r="F9" t="n">
-        <v>42.23896</v>
+        <v>56.66501</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04995</v>
+        <v>42.29035</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81963</v>
+        <v>83.75954</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05134</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.81684</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.45522</v>
+        <v>16.71462</v>
       </c>
       <c r="D10" t="n">
-        <v>16.2964</v>
+        <v>16.41761</v>
       </c>
       <c r="E10" t="n">
-        <v>16.4941</v>
+        <v>16.56927</v>
       </c>
       <c r="F10" t="n">
-        <v>42.57525</v>
+        <v>56.25427</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04988</v>
+        <v>41.88798</v>
       </c>
       <c r="H10" t="n">
-        <v>1.77389</v>
+        <v>84.55793</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.79193</v>
       </c>
     </row>
     <row r="11">
@@ -696,15 +760,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -722,22 +796,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.05827</v>
+        <v>16.94276</v>
       </c>
       <c r="D12" t="n">
-        <v>16.68479</v>
+        <v>16.3075</v>
       </c>
       <c r="E12" t="n">
-        <v>17.15753</v>
+        <v>16.50849</v>
       </c>
       <c r="F12" t="n">
-        <v>44.14174</v>
+        <v>56.50572</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04994</v>
+        <v>42.06204</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7958</v>
+        <v>86.56198999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.83989</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.58692</v>
+        <v>16.75892</v>
       </c>
       <c r="D13" t="n">
-        <v>16.739</v>
+        <v>16.53386</v>
       </c>
       <c r="E13" t="n">
-        <v>16.93216</v>
+        <v>16.57045</v>
       </c>
       <c r="F13" t="n">
-        <v>43.03326</v>
+        <v>55.81954</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05138</v>
+        <v>42.35588</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81651</v>
+        <v>82.31188</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.83791</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.69004</v>
+        <v>16.85126</v>
       </c>
       <c r="D14" t="n">
-        <v>16.51626</v>
+        <v>16.49105</v>
       </c>
       <c r="E14" t="n">
-        <v>16.84381</v>
+        <v>16.63443</v>
       </c>
       <c r="F14" t="n">
-        <v>42.34385</v>
+        <v>55.52527</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05028</v>
+        <v>42.01434</v>
       </c>
       <c r="H14" t="n">
-        <v>1.80952</v>
+        <v>84.13505000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.84242</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.17052</v>
+        <v>16.89176</v>
       </c>
       <c r="D15" t="n">
-        <v>16.72455</v>
+        <v>16.56944</v>
       </c>
       <c r="E15" t="n">
-        <v>16.83502</v>
+        <v>16.64812</v>
       </c>
       <c r="F15" t="n">
-        <v>41.91982</v>
+        <v>55.42896</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04974</v>
+        <v>42.47667</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85449</v>
+        <v>84.12163</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05165</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.8124</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.71476</v>
+        <v>16.86803</v>
       </c>
       <c r="D16" t="n">
-        <v>16.35305</v>
+        <v>16.32669</v>
       </c>
       <c r="E16" t="n">
-        <v>16.94174</v>
+        <v>16.75193</v>
       </c>
       <c r="F16" t="n">
-        <v>42.39305</v>
+        <v>55.05738</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05035</v>
+        <v>42.74123</v>
       </c>
       <c r="H16" t="n">
-        <v>1.80193</v>
+        <v>85.08214</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.04997</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.82151</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.66969</v>
+        <v>16.73459</v>
       </c>
       <c r="D17" t="n">
-        <v>16.774</v>
+        <v>16.39649</v>
       </c>
       <c r="E17" t="n">
-        <v>16.45599</v>
+        <v>16.69484</v>
       </c>
       <c r="F17" t="n">
-        <v>42.27896</v>
+        <v>56.71819</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05152</v>
+        <v>42.21085</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79193</v>
+        <v>86.42910999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.82455</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.50849</v>
+        <v>16.71457</v>
       </c>
       <c r="D18" t="n">
-        <v>16.94276</v>
+        <v>16.40936</v>
       </c>
       <c r="E18" t="n">
-        <v>16.3075</v>
+        <v>16.69531</v>
       </c>
       <c r="F18" t="n">
-        <v>43.14982</v>
+        <v>55.90706</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05007</v>
+        <v>42.14551</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8549</v>
+        <v>83.04597</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05106</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.77553</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.88738</v>
+        <v>16.8682</v>
       </c>
       <c r="D19" t="n">
-        <v>16.76346</v>
+        <v>16.47266</v>
       </c>
       <c r="E19" t="n">
-        <v>16.65797</v>
+        <v>16.55288</v>
       </c>
       <c r="F19" t="n">
-        <v>42.3428</v>
+        <v>55.15421</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05021</v>
+        <v>42.27943</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82682</v>
+        <v>85.03135</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05067</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.83892</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +1044,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.74066</v>
+        <v>16.9819</v>
       </c>
       <c r="D20" t="n">
-        <v>16.07041</v>
+        <v>16.67436</v>
       </c>
       <c r="E20" t="n">
-        <v>16.61425</v>
+        <v>16.82209</v>
       </c>
       <c r="F20" t="n">
-        <v>42.88466</v>
+        <v>56.15902</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05076</v>
+        <v>42.37933</v>
       </c>
       <c r="H20" t="n">
-        <v>1.80999</v>
+        <v>82.98771000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.79026</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +1086,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -970,20 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.62628</v>
+        <v>16.62328</v>
       </c>
       <c r="D22" t="n">
-        <v>15.54708</v>
+        <v>16.14922</v>
       </c>
       <c r="E22" t="n">
-        <v>15.45527</v>
+        <v>16.37423</v>
       </c>
       <c r="F22" t="n">
-        <v>251.8042</v>
+        <v>21.61182</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34.44194</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.74518</v>
+        <v>16.67089</v>
       </c>
       <c r="D23" t="n">
-        <v>15.76294</v>
+        <v>16.12756</v>
       </c>
       <c r="E23" t="n">
-        <v>15.72155</v>
+        <v>16.28724</v>
       </c>
       <c r="F23" t="n">
-        <v>255.20357</v>
+        <v>21.85062</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33.58561</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.56523</v>
+        <v>16.52868</v>
       </c>
       <c r="D24" t="n">
-        <v>15.52011</v>
+        <v>15.84983</v>
       </c>
       <c r="E24" t="n">
-        <v>15.62535</v>
+        <v>16.24199</v>
       </c>
       <c r="F24" t="n">
-        <v>251.76403</v>
+        <v>21.47281</v>
+      </c>
+      <c r="G24" t="n">
+        <v>34.61454</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.01053</v>
+        <v>16.50673</v>
       </c>
       <c r="D25" t="n">
-        <v>15.50613</v>
+        <v>16.08485</v>
       </c>
       <c r="E25" t="n">
-        <v>15.69946</v>
+        <v>16.17777</v>
       </c>
       <c r="F25" t="n">
-        <v>250.27615</v>
+        <v>21.30641</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.72362</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.73666</v>
+        <v>16.65226</v>
       </c>
       <c r="D26" t="n">
-        <v>15.41607</v>
+        <v>15.43976</v>
       </c>
       <c r="E26" t="n">
-        <v>15.72267</v>
+        <v>16.62321</v>
       </c>
       <c r="F26" t="n">
-        <v>254.63868</v>
+        <v>21.63437</v>
+      </c>
+      <c r="G26" t="n">
+        <v>33.89899</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.49139</v>
+        <v>16.82302</v>
       </c>
       <c r="D27" t="n">
-        <v>15.58406</v>
+        <v>16.30809</v>
       </c>
       <c r="E27" t="n">
-        <v>15.57526</v>
+        <v>16.56247</v>
       </c>
       <c r="F27" t="n">
-        <v>255.91961</v>
+        <v>21.5787</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34.02836</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.40276</v>
+        <v>16.7505</v>
       </c>
       <c r="D28" t="n">
-        <v>15.88109</v>
+        <v>15.80677</v>
       </c>
       <c r="E28" t="n">
-        <v>15.52756</v>
+        <v>16.23277</v>
       </c>
       <c r="F28" t="n">
-        <v>258.66998</v>
+        <v>22.1004</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.27092</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.57683</v>
+        <v>16.98999</v>
       </c>
       <c r="D29" t="n">
-        <v>15.61004</v>
+        <v>15.93887</v>
       </c>
       <c r="E29" t="n">
-        <v>15.5387</v>
+        <v>16.41356</v>
       </c>
       <c r="F29" t="n">
-        <v>251.54355</v>
+        <v>22.40831</v>
+      </c>
+      <c r="G29" t="n">
+        <v>34.55992</v>
       </c>
     </row>
     <row r="30">
@@ -1126,42 +1283,60 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.70157</v>
+        <v>16.72972</v>
       </c>
       <c r="D30" t="n">
-        <v>15.65398</v>
+        <v>15.73142</v>
       </c>
       <c r="E30" t="n">
-        <v>15.50353</v>
+        <v>16.1397</v>
       </c>
       <c r="F30" t="n">
-        <v>248.54473</v>
+        <v>21.89931</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34.11763</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Rz mean</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Rz min</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Rz max</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
         </is>
       </c>
     </row>
@@ -1173,23 +1348,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.84946</v>
+        <v>0.76298</v>
       </c>
       <c r="D32" t="n">
-        <v>15.58522</v>
+        <v>0.08016</v>
       </c>
       <c r="E32" t="n">
-        <v>16.46174</v>
+        <v>0.60984</v>
       </c>
       <c r="F32" t="n">
-        <v>21.59526</v>
+        <v>0.95807</v>
       </c>
       <c r="G32" t="n">
-        <v>33.90833</v>
+        <v>0.11044</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09268999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1263</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1383,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.54626</v>
+        <v>0.76297</v>
       </c>
       <c r="D33" t="n">
-        <v>15.90512</v>
+        <v>0.08013000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>16.3989</v>
+        <v>0.61139</v>
       </c>
       <c r="F33" t="n">
-        <v>21.78796</v>
+        <v>0.94296</v>
       </c>
       <c r="G33" t="n">
-        <v>34.53092</v>
+        <v>0.11053</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09061</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12652</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1414,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.72075</v>
+        <v>0.74679</v>
       </c>
       <c r="D34" t="n">
-        <v>16.06432</v>
+        <v>0.08137999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>16.67314</v>
+        <v>0.6091</v>
       </c>
       <c r="F34" t="n">
-        <v>21.95307</v>
+        <v>0.96293</v>
       </c>
       <c r="G34" t="n">
-        <v>34.10527</v>
+        <v>0.11111</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09322</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12999</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1445,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.30116</v>
+        <v>0.75207</v>
       </c>
       <c r="D35" t="n">
-        <v>15.92255</v>
+        <v>0.08121</v>
       </c>
       <c r="E35" t="n">
-        <v>16.11233</v>
+        <v>0.60642</v>
       </c>
       <c r="F35" t="n">
-        <v>21.66063</v>
+        <v>0.97155</v>
       </c>
       <c r="G35" t="n">
-        <v>34.54706</v>
+        <v>0.11124</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09198000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12553</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1476,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.67746</v>
+        <v>0.75753</v>
       </c>
       <c r="D36" t="n">
-        <v>15.88217</v>
+        <v>0.08137</v>
       </c>
       <c r="E36" t="n">
-        <v>16.50768</v>
+        <v>0.60807</v>
       </c>
       <c r="F36" t="n">
-        <v>21.72268</v>
+        <v>0.96904</v>
       </c>
       <c r="G36" t="n">
-        <v>34.84232</v>
+        <v>0.10861</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09319</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12375</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1507,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.42622</v>
+        <v>0.75903</v>
       </c>
       <c r="D37" t="n">
-        <v>16.05766</v>
+        <v>0.08096</v>
       </c>
       <c r="E37" t="n">
-        <v>16.09724</v>
+        <v>0.60361</v>
       </c>
       <c r="F37" t="n">
-        <v>21.1638</v>
+        <v>0.96793</v>
       </c>
       <c r="G37" t="n">
-        <v>33.90659</v>
+        <v>0.11062</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09279</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12821</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1538,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.83477</v>
+        <v>0.74594</v>
       </c>
       <c r="D38" t="n">
-        <v>15.78002</v>
+        <v>0.07883999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>16.5904</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>21.50877</v>
+        <v>0.93333</v>
       </c>
       <c r="G38" t="n">
-        <v>34.60813</v>
+        <v>0.11178</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09334000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12411</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1569,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.38272</v>
+        <v>0.74783</v>
       </c>
       <c r="D39" t="n">
-        <v>15.65773</v>
+        <v>0.08185000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>16.64268</v>
+        <v>0.60897</v>
       </c>
       <c r="F39" t="n">
-        <v>21.6984</v>
+        <v>0.97798</v>
       </c>
       <c r="G39" t="n">
-        <v>33.02937</v>
+        <v>0.11142</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09347999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12239</v>
       </c>
     </row>
     <row r="40">
@@ -1353,843 +1600,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.93105</v>
+        <v>0.7340100000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>15.89875</v>
+        <v>0.08076</v>
       </c>
       <c r="E40" t="n">
-        <v>16.24744</v>
+        <v>0.61078</v>
       </c>
       <c r="F40" t="n">
-        <v>21.92091</v>
+        <v>0.95558</v>
       </c>
       <c r="G40" t="n">
-        <v>34.88692</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Trace 2</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>16.86918</v>
-      </c>
-      <c r="D42" t="n">
-        <v>15.85784</v>
-      </c>
-      <c r="E42" t="n">
-        <v>16.30945</v>
-      </c>
-      <c r="F42" t="n">
-        <v>21.8264</v>
-      </c>
-      <c r="G42" t="n">
-        <v>33.81448</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>16.53338</v>
-      </c>
-      <c r="D43" t="n">
-        <v>16.24122</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16.42571</v>
-      </c>
-      <c r="F43" t="n">
-        <v>22.13847</v>
-      </c>
-      <c r="G43" t="n">
-        <v>34.09708</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>16.71752</v>
-      </c>
-      <c r="D44" t="n">
-        <v>16.4675</v>
-      </c>
-      <c r="E44" t="n">
-        <v>16.56422</v>
-      </c>
-      <c r="F44" t="n">
-        <v>21.79933</v>
-      </c>
-      <c r="G44" t="n">
-        <v>33.6533</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>16.43858</v>
-      </c>
-      <c r="D45" t="n">
-        <v>16.09345</v>
-      </c>
-      <c r="E45" t="n">
-        <v>16.35223</v>
-      </c>
-      <c r="F45" t="n">
-        <v>22.16758</v>
-      </c>
-      <c r="G45" t="n">
-        <v>33.86618</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>16.77052</v>
-      </c>
-      <c r="D46" t="n">
-        <v>15.93416</v>
-      </c>
-      <c r="E46" t="n">
-        <v>16.56617</v>
-      </c>
-      <c r="F46" t="n">
-        <v>21.9023</v>
-      </c>
-      <c r="G46" t="n">
-        <v>34.05513</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>16.67187</v>
-      </c>
-      <c r="D47" t="n">
-        <v>16.29054</v>
-      </c>
-      <c r="E47" t="n">
-        <v>16.22535</v>
-      </c>
-      <c r="F47" t="n">
-        <v>21.90802</v>
-      </c>
-      <c r="G47" t="n">
-        <v>33.54952</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>16.88587</v>
-      </c>
-      <c r="D48" t="n">
-        <v>15.89037</v>
-      </c>
-      <c r="E48" t="n">
-        <v>15.95494</v>
-      </c>
-      <c r="F48" t="n">
-        <v>21.76094</v>
-      </c>
-      <c r="G48" t="n">
-        <v>34.10992</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>16.78524</v>
-      </c>
-      <c r="D49" t="n">
-        <v>16.03957</v>
-      </c>
-      <c r="E49" t="n">
-        <v>16.42042</v>
-      </c>
-      <c r="F49" t="n">
-        <v>22.11985</v>
-      </c>
-      <c r="G49" t="n">
-        <v>34.20674</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>16.71886</v>
-      </c>
-      <c r="D50" t="n">
-        <v>16.43077</v>
-      </c>
-      <c r="E50" t="n">
-        <v>16.46428</v>
-      </c>
-      <c r="F50" t="n">
-        <v>21.82475</v>
-      </c>
-      <c r="G50" t="n">
-        <v>34.16147</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.61361</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1.13301</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.60687</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.09976</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.60256</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.12605</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.61029</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.11479</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.61202</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1.10622</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.61459</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.11424</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.59398</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1.12829</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.60721</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1.10661</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.61133</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.12667</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via 2</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0.61172</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.10949</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0.6153999999999999</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.10883</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0.59131</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.11541</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0.58947</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.13852</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.60878</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.11603</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0.59572</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.11163</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0.61386</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.11644</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0.6176700000000001</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.13485</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0.59976</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1.11767</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>0.72457</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.07935</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.60567</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.96707</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.10863</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.09307</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.12621</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0.75947</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.07998</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.60251</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.96026</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.10697</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.09546</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.12766</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.08148</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.61182</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.97576</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.10946</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.09474</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.12658</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>0.74234</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.08266</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.61217</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.94961</v>
-      </c>
-      <c r="G75" t="n">
         <v>0.10914</v>
       </c>
-      <c r="H75" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.12505</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>0.76192</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.08069999999999999</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.59534</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.96134</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.1097</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.09224</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.12796</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0.75546</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.07986</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.6137</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.96674</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.10963</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.09318</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.1253</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>0.7613</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.08105999999999999</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.5986399999999999</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.95195</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.11014</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.09396</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.12851</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>0.7474499999999999</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.07968</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.59759</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0.97495</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0.10799</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.00738</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.09379</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.12503</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.75573</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.08015</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.60307</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.95318</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.10963</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.00746</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.09433999999999999</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.12611</v>
+      <c r="H40" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09289</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12829</v>
       </c>
     </row>
   </sheetData>
